--- a/Assets/결과/#2 장애물 작은 거/TestControllerAgent_MissReward(Clone)1_vs_TestTotalAgent_MissReward(Clone)2.xlsx
+++ b/Assets/결과/#2 장애물 작은 거/TestControllerAgent_MissReward(Clone)1_vs_TestTotalAgent_MissReward(Clone)2.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltrn\Github\Unity-MLAgents-FPS\Assets\결과\#2 장애물 작은 거\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B37F8A82-FD59-415E-B209-D55BD11E7738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C1C952-440E-495D-93A6-08A3DE2C053E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="3720" windowWidth="15792" windowHeight="9960" xr2:uid="{03CE7035-1576-44C3-BED2-BEC47B2244B5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{03CE7035-1576-44C3-BED2-BEC47B2244B5}"/>
   </bookViews>
   <sheets>
     <sheet name="TestControllerAgent_MissReward(" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -688,7 +701,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCEE6148-2926-495C-9181-5711CEFF21C7}" name="표1" displayName="표1" ref="A1:G2001" totalsRowShown="0">
-  <autoFilter ref="A1:G2001" xr:uid="{DCEE6148-2926-495C-9181-5711CEFF21C7}"/>
+  <autoFilter ref="A1:G2001" xr:uid="{DCEE6148-2926-495C-9181-5711CEFF21C7}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="TestControllerAgent_MissReward(Clone)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D6D89E5C-3F6E-40D4-B71C-CD8AC7A259E7}" name="열1"/>
     <tableColumn id="2" xr3:uid="{AB65A18A-C734-4AC0-831D-F9E175A0EC0B}" name="열2"/>
@@ -1068,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1114,7 +1133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1160,7 +1179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1206,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1252,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5</v>
       </c>
@@ -1298,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
@@ -1344,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7</v>
       </c>
@@ -1390,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>8</v>
       </c>
@@ -1436,7 +1455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9</v>
       </c>
@@ -1482,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10</v>
       </c>
@@ -1528,7 +1547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>11</v>
       </c>
@@ -1574,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
@@ -1620,7 +1639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>13</v>
       </c>
@@ -1666,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14</v>
       </c>
@@ -1712,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>15</v>
       </c>
@@ -1758,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>16</v>
       </c>
@@ -1804,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>17</v>
       </c>
@@ -1850,7 +1869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>18</v>
       </c>
@@ -1896,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>19</v>
       </c>
@@ -1942,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20</v>
       </c>
@@ -1988,7 +2007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>21</v>
       </c>
@@ -2034,7 +2053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>22</v>
       </c>
@@ -2080,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>23</v>
       </c>
@@ -2126,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>24</v>
       </c>
@@ -2172,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>25</v>
       </c>
@@ -2218,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>26</v>
       </c>
@@ -2264,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>27</v>
       </c>
@@ -2310,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>28</v>
       </c>
@@ -2356,7 +2375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>29</v>
       </c>
@@ -2402,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>30</v>
       </c>
@@ -2448,7 +2467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>31</v>
       </c>
@@ -2494,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>32</v>
       </c>
@@ -2540,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>33</v>
       </c>
@@ -2586,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>34</v>
       </c>
@@ -2632,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>35</v>
       </c>
@@ -2678,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>36</v>
       </c>
@@ -2724,7 +2743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>37</v>
       </c>
@@ -2770,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>38</v>
       </c>
@@ -2816,7 +2835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>39</v>
       </c>
@@ -2862,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>40</v>
       </c>
@@ -2908,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>41</v>
       </c>
@@ -2954,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>42</v>
       </c>
@@ -3000,7 +3019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>43</v>
       </c>
@@ -3046,7 +3065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>44</v>
       </c>
@@ -3092,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>45</v>
       </c>
@@ -3138,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>46</v>
       </c>
@@ -3184,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>47</v>
       </c>
@@ -3230,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>48</v>
       </c>
@@ -3276,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>49</v>
       </c>
@@ -3322,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>50</v>
       </c>
@@ -3368,7 +3387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>51</v>
       </c>
@@ -3414,7 +3433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>52</v>
       </c>
@@ -3460,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>53</v>
       </c>
@@ -3506,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>54</v>
       </c>
@@ -3552,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>55</v>
       </c>
@@ -3598,7 +3617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>56</v>
       </c>
@@ -3644,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>57</v>
       </c>
@@ -3690,7 +3709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>58</v>
       </c>
@@ -3736,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>59</v>
       </c>
@@ -3782,7 +3801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>60</v>
       </c>
@@ -3828,7 +3847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>61</v>
       </c>
@@ -3874,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>62</v>
       </c>
@@ -3920,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>63</v>
       </c>
@@ -3966,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>64</v>
       </c>
@@ -4012,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>65</v>
       </c>
@@ -4058,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>66</v>
       </c>
@@ -4104,7 +4123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>67</v>
       </c>
@@ -4150,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>68</v>
       </c>
@@ -4196,7 +4215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>69</v>
       </c>
@@ -4242,7 +4261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>70</v>
       </c>
@@ -4288,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>71</v>
       </c>
@@ -4334,7 +4353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>72</v>
       </c>
@@ -4380,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>73</v>
       </c>
@@ -4426,7 +4445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>74</v>
       </c>
@@ -4472,7 +4491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>75</v>
       </c>
@@ -4518,7 +4537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>76</v>
       </c>
@@ -4564,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>77</v>
       </c>
@@ -4610,7 +4629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>78</v>
       </c>
@@ -4656,7 +4675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>79</v>
       </c>
@@ -4702,7 +4721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>80</v>
       </c>
@@ -4748,7 +4767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>81</v>
       </c>
@@ -4794,7 +4813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>82</v>
       </c>
@@ -4840,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>83</v>
       </c>
@@ -4886,7 +4905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>84</v>
       </c>
@@ -4932,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>85</v>
       </c>
@@ -4978,7 +4997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>86</v>
       </c>
@@ -5024,7 +5043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>87</v>
       </c>
@@ -5070,7 +5089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>88</v>
       </c>
@@ -5116,7 +5135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>89</v>
       </c>
@@ -5162,7 +5181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>90</v>
       </c>
@@ -5208,7 +5227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>91</v>
       </c>
@@ -5254,7 +5273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>92</v>
       </c>
@@ -5300,7 +5319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>93</v>
       </c>
@@ -5346,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>94</v>
       </c>
@@ -5392,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>95</v>
       </c>
@@ -5438,7 +5457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>96</v>
       </c>
@@ -5484,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>97</v>
       </c>
@@ -5530,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>98</v>
       </c>
@@ -5576,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>99</v>
       </c>
@@ -5622,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>100</v>
       </c>
@@ -5668,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>101</v>
       </c>
@@ -5714,7 +5733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>102</v>
       </c>
@@ -5760,7 +5779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>103</v>
       </c>
@@ -5806,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>104</v>
       </c>
@@ -5852,7 +5871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>105</v>
       </c>
@@ -5898,7 +5917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>106</v>
       </c>
@@ -5944,7 +5963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>107</v>
       </c>
@@ -5990,7 +6009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>108</v>
       </c>
@@ -6036,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>109</v>
       </c>
@@ -6082,7 +6101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>110</v>
       </c>
@@ -6128,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>111</v>
       </c>
@@ -6174,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>112</v>
       </c>
@@ -6220,7 +6239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>113</v>
       </c>
@@ -6266,7 +6285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>114</v>
       </c>
@@ -6312,7 +6331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>115</v>
       </c>
@@ -6358,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>116</v>
       </c>
@@ -6404,7 +6423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>117</v>
       </c>
@@ -6450,7 +6469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>118</v>
       </c>
@@ -6496,7 +6515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>119</v>
       </c>
@@ -6542,7 +6561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>120</v>
       </c>
@@ -6588,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>121</v>
       </c>
@@ -6634,7 +6653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>122</v>
       </c>
@@ -6680,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>123</v>
       </c>
@@ -6726,7 +6745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>124</v>
       </c>
@@ -6772,7 +6791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>125</v>
       </c>
@@ -6818,7 +6837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>126</v>
       </c>
@@ -6864,7 +6883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>127</v>
       </c>
@@ -6910,7 +6929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>128</v>
       </c>
@@ -6956,7 +6975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>129</v>
       </c>
@@ -7002,7 +7021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>130</v>
       </c>
@@ -7048,7 +7067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>131</v>
       </c>
@@ -7094,7 +7113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>132</v>
       </c>
@@ -7140,7 +7159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>133</v>
       </c>
@@ -7186,7 +7205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>134</v>
       </c>
@@ -7232,7 +7251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>135</v>
       </c>
@@ -7278,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>136</v>
       </c>
@@ -7324,7 +7343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>137</v>
       </c>
@@ -7370,7 +7389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>138</v>
       </c>
@@ -7416,7 +7435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>139</v>
       </c>
@@ -7462,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>140</v>
       </c>
@@ -7508,7 +7527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>141</v>
       </c>
@@ -7554,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>142</v>
       </c>
@@ -7600,7 +7619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>143</v>
       </c>
@@ -7646,7 +7665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>144</v>
       </c>
@@ -7692,7 +7711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>145</v>
       </c>
@@ -7738,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>146</v>
       </c>
@@ -7784,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>147</v>
       </c>
@@ -7830,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>148</v>
       </c>
@@ -7876,7 +7895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>149</v>
       </c>
@@ -7922,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>150</v>
       </c>
@@ -7968,7 +7987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>151</v>
       </c>
@@ -8014,7 +8033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>152</v>
       </c>
@@ -8060,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>153</v>
       </c>
@@ -8106,7 +8125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>154</v>
       </c>
@@ -8152,7 +8171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>155</v>
       </c>
@@ -8198,7 +8217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>156</v>
       </c>
@@ -8244,7 +8263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>157</v>
       </c>
@@ -8290,7 +8309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>158</v>
       </c>
@@ -8336,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>159</v>
       </c>
@@ -8382,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>160</v>
       </c>
@@ -8428,7 +8447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>161</v>
       </c>
@@ -8474,7 +8493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>162</v>
       </c>
@@ -8520,7 +8539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>163</v>
       </c>
@@ -8566,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>164</v>
       </c>
@@ -8612,7 +8631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>165</v>
       </c>
@@ -8658,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>166</v>
       </c>
@@ -8704,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>167</v>
       </c>
@@ -8750,7 +8769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>168</v>
       </c>
@@ -8796,7 +8815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>169</v>
       </c>
@@ -8842,7 +8861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>170</v>
       </c>
@@ -8888,7 +8907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>171</v>
       </c>
@@ -8934,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>172</v>
       </c>
@@ -8980,7 +8999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>173</v>
       </c>
@@ -9026,7 +9045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>174</v>
       </c>
@@ -9072,7 +9091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>175</v>
       </c>
@@ -9118,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>176</v>
       </c>
@@ -9164,7 +9183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>177</v>
       </c>
@@ -9210,7 +9229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>178</v>
       </c>
@@ -9256,7 +9275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>179</v>
       </c>
@@ -9302,7 +9321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>180</v>
       </c>
@@ -9348,7 +9367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>181</v>
       </c>
@@ -9394,7 +9413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>182</v>
       </c>
@@ -9440,7 +9459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>183</v>
       </c>
@@ -9486,7 +9505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>184</v>
       </c>
@@ -9532,7 +9551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>185</v>
       </c>
@@ -9578,7 +9597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>186</v>
       </c>
@@ -9624,7 +9643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>187</v>
       </c>
@@ -9670,7 +9689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>188</v>
       </c>
@@ -9716,7 +9735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>189</v>
       </c>
@@ -9762,7 +9781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>190</v>
       </c>
@@ -9808,7 +9827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>191</v>
       </c>
@@ -9854,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>192</v>
       </c>
@@ -9900,7 +9919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>193</v>
       </c>
@@ -9946,7 +9965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>194</v>
       </c>
@@ -9992,7 +10011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>195</v>
       </c>
@@ -10038,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>196</v>
       </c>
@@ -10084,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>197</v>
       </c>
@@ -10130,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>198</v>
       </c>
@@ -10176,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>199</v>
       </c>
@@ -10222,7 +10241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>200</v>
       </c>
@@ -10268,7 +10287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>201</v>
       </c>
@@ -10314,7 +10333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>202</v>
       </c>
@@ -10360,7 +10379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>203</v>
       </c>
@@ -10406,7 +10425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>204</v>
       </c>
@@ -10452,7 +10471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>205</v>
       </c>
@@ -10498,7 +10517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>206</v>
       </c>
@@ -10544,7 +10563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>207</v>
       </c>
@@ -10590,7 +10609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>208</v>
       </c>
@@ -10636,7 +10655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>209</v>
       </c>
@@ -10682,7 +10701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>210</v>
       </c>
@@ -10728,7 +10747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>211</v>
       </c>
@@ -10774,7 +10793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>212</v>
       </c>
@@ -10820,7 +10839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>213</v>
       </c>
@@ -10866,7 +10885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>214</v>
       </c>
@@ -10912,7 +10931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>215</v>
       </c>
@@ -10958,7 +10977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>216</v>
       </c>
@@ -11004,7 +11023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>217</v>
       </c>
@@ -11050,7 +11069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>218</v>
       </c>
@@ -11096,7 +11115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>219</v>
       </c>
@@ -11142,7 +11161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>220</v>
       </c>
@@ -11188,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>221</v>
       </c>
@@ -11234,7 +11253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>222</v>
       </c>
@@ -11280,7 +11299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>223</v>
       </c>
@@ -11326,7 +11345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>224</v>
       </c>
@@ -11372,7 +11391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>225</v>
       </c>
@@ -11418,7 +11437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>226</v>
       </c>
@@ -11464,7 +11483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>227</v>
       </c>
@@ -11510,7 +11529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>228</v>
       </c>
@@ -11556,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>229</v>
       </c>
@@ -11602,7 +11621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>230</v>
       </c>
@@ -11648,7 +11667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>231</v>
       </c>
@@ -11694,7 +11713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>232</v>
       </c>
@@ -11740,7 +11759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>233</v>
       </c>
@@ -11786,7 +11805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>234</v>
       </c>
@@ -11832,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>235</v>
       </c>
@@ -11878,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>236</v>
       </c>
@@ -11924,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>237</v>
       </c>
@@ -11970,7 +11989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>238</v>
       </c>
@@ -12016,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>239</v>
       </c>
@@ -12062,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>240</v>
       </c>
@@ -12108,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>241</v>
       </c>
@@ -12154,7 +12173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>242</v>
       </c>
@@ -12200,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>243</v>
       </c>
@@ -12246,7 +12265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>244</v>
       </c>
@@ -12292,7 +12311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>245</v>
       </c>
@@ -12338,7 +12357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>246</v>
       </c>
@@ -12384,7 +12403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>247</v>
       </c>
@@ -12430,7 +12449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>248</v>
       </c>
@@ -12476,7 +12495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>249</v>
       </c>
@@ -12522,7 +12541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>250</v>
       </c>
@@ -12568,7 +12587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>251</v>
       </c>
@@ -12614,7 +12633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>252</v>
       </c>
@@ -12660,7 +12679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>253</v>
       </c>
@@ -12706,7 +12725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>254</v>
       </c>
@@ -12752,7 +12771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>255</v>
       </c>
@@ -12798,7 +12817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>256</v>
       </c>
@@ -12844,7 +12863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>257</v>
       </c>
@@ -12890,7 +12909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>258</v>
       </c>
@@ -12936,7 +12955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>259</v>
       </c>
@@ -12982,7 +13001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>260</v>
       </c>
@@ -13028,7 +13047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>261</v>
       </c>
@@ -13074,7 +13093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>262</v>
       </c>
@@ -13120,7 +13139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>263</v>
       </c>
@@ -13166,7 +13185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>264</v>
       </c>
@@ -13212,7 +13231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>265</v>
       </c>
@@ -13258,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>266</v>
       </c>
@@ -13304,7 +13323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>267</v>
       </c>
@@ -13350,7 +13369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>268</v>
       </c>
@@ -13396,7 +13415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>269</v>
       </c>
@@ -13442,7 +13461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>270</v>
       </c>
@@ -13488,7 +13507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>271</v>
       </c>
@@ -13534,7 +13553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>272</v>
       </c>
@@ -13580,7 +13599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>273</v>
       </c>
@@ -13626,7 +13645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>274</v>
       </c>
@@ -13672,7 +13691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>275</v>
       </c>
@@ -13718,7 +13737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>276</v>
       </c>
@@ -13764,7 +13783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>277</v>
       </c>
@@ -13810,7 +13829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>278</v>
       </c>
@@ -13856,7 +13875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>279</v>
       </c>
@@ -13902,7 +13921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>280</v>
       </c>
@@ -13948,7 +13967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>281</v>
       </c>
@@ -13994,7 +14013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>282</v>
       </c>
@@ -14040,7 +14059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>283</v>
       </c>
@@ -14086,7 +14105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>284</v>
       </c>
@@ -14132,7 +14151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>285</v>
       </c>
@@ -14178,7 +14197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>286</v>
       </c>
@@ -14224,7 +14243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>287</v>
       </c>
@@ -14270,7 +14289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>288</v>
       </c>
@@ -14316,7 +14335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>289</v>
       </c>
@@ -14362,7 +14381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>290</v>
       </c>
@@ -14408,7 +14427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>291</v>
       </c>
@@ -14454,7 +14473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>292</v>
       </c>
@@ -14500,7 +14519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>293</v>
       </c>
@@ -14546,7 +14565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>294</v>
       </c>
@@ -14592,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>295</v>
       </c>
@@ -14638,7 +14657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>296</v>
       </c>
@@ -14684,7 +14703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>297</v>
       </c>
@@ -14730,7 +14749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>298</v>
       </c>
@@ -14776,7 +14795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>299</v>
       </c>
@@ -14822,7 +14841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>300</v>
       </c>
@@ -14868,7 +14887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>301</v>
       </c>
@@ -14914,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>302</v>
       </c>
@@ -14960,7 +14979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>303</v>
       </c>
@@ -15006,7 +15025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>304</v>
       </c>
@@ -15052,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>305</v>
       </c>
@@ -15098,7 +15117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>306</v>
       </c>
@@ -15144,7 +15163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>307</v>
       </c>
@@ -15190,7 +15209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>308</v>
       </c>
@@ -15236,7 +15255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>309</v>
       </c>
@@ -15282,7 +15301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>310</v>
       </c>
@@ -15328,7 +15347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>311</v>
       </c>
@@ -15374,7 +15393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>312</v>
       </c>
@@ -15420,7 +15439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>313</v>
       </c>
@@ -15466,7 +15485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>314</v>
       </c>
@@ -15512,7 +15531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>315</v>
       </c>
@@ -15558,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>316</v>
       </c>
@@ -15604,7 +15623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>317</v>
       </c>
@@ -15650,7 +15669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>318</v>
       </c>
@@ -15696,7 +15715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>319</v>
       </c>
@@ -15742,7 +15761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>320</v>
       </c>
@@ -15788,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>321</v>
       </c>
@@ -15834,7 +15853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>322</v>
       </c>
@@ -15880,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>323</v>
       </c>
@@ -15926,7 +15945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>324</v>
       </c>
@@ -15972,7 +15991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>325</v>
       </c>
@@ -16018,7 +16037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>326</v>
       </c>
@@ -16064,7 +16083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>327</v>
       </c>
@@ -16110,7 +16129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>328</v>
       </c>
@@ -16156,7 +16175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>329</v>
       </c>
@@ -16202,7 +16221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>330</v>
       </c>
@@ -16248,7 +16267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>331</v>
       </c>
@@ -16294,7 +16313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>332</v>
       </c>
@@ -16340,7 +16359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>333</v>
       </c>
@@ -16386,7 +16405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>334</v>
       </c>
@@ -16432,7 +16451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>335</v>
       </c>
@@ -16478,7 +16497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>336</v>
       </c>
@@ -16524,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>337</v>
       </c>
@@ -16570,7 +16589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>338</v>
       </c>
@@ -16616,7 +16635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>339</v>
       </c>
@@ -16662,7 +16681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>340</v>
       </c>
@@ -16708,7 +16727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>341</v>
       </c>
@@ -16754,7 +16773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>342</v>
       </c>
@@ -16800,7 +16819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>343</v>
       </c>
@@ -16846,7 +16865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>344</v>
       </c>
@@ -16892,7 +16911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>345</v>
       </c>
@@ -16938,7 +16957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>346</v>
       </c>
@@ -16984,7 +17003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>347</v>
       </c>
@@ -17030,7 +17049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>348</v>
       </c>
@@ -17076,7 +17095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>349</v>
       </c>
@@ -17122,7 +17141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>350</v>
       </c>
@@ -17168,7 +17187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>351</v>
       </c>
@@ -17214,7 +17233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>352</v>
       </c>
@@ -17260,7 +17279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>353</v>
       </c>
@@ -17306,7 +17325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>354</v>
       </c>
@@ -17352,7 +17371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>355</v>
       </c>
@@ -17398,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>356</v>
       </c>
@@ -17444,7 +17463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>357</v>
       </c>
@@ -17490,7 +17509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>358</v>
       </c>
@@ -17536,7 +17555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>359</v>
       </c>
@@ -17582,7 +17601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>360</v>
       </c>
@@ -17628,7 +17647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>361</v>
       </c>
@@ -17674,7 +17693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>362</v>
       </c>
@@ -17720,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>363</v>
       </c>
@@ -17766,7 +17785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>364</v>
       </c>
@@ -17812,7 +17831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>365</v>
       </c>
@@ -17858,7 +17877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>366</v>
       </c>
@@ -17904,7 +17923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>367</v>
       </c>
@@ -17950,7 +17969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>368</v>
       </c>
@@ -17996,7 +18015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>369</v>
       </c>
@@ -18042,7 +18061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>370</v>
       </c>
@@ -18088,7 +18107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>371</v>
       </c>
@@ -18134,7 +18153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>372</v>
       </c>
@@ -18180,7 +18199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747">
         <v>373</v>
       </c>
@@ -18226,7 +18245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>374</v>
       </c>
@@ -18272,7 +18291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>375</v>
       </c>
@@ -18318,7 +18337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>376</v>
       </c>
@@ -18364,7 +18383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>377</v>
       </c>
@@ -18410,7 +18429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>378</v>
       </c>
@@ -18456,7 +18475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>379</v>
       </c>
@@ -18502,7 +18521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761">
         <v>380</v>
       </c>
@@ -18548,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763">
         <v>381</v>
       </c>
@@ -18594,7 +18613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>382</v>
       </c>
@@ -18640,7 +18659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>383</v>
       </c>
@@ -18686,7 +18705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>384</v>
       </c>
@@ -18732,7 +18751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>385</v>
       </c>
@@ -18778,7 +18797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>386</v>
       </c>
@@ -18824,7 +18843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>387</v>
       </c>
@@ -18870,7 +18889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>388</v>
       </c>
@@ -18916,7 +18935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>389</v>
       </c>
@@ -18962,7 +18981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>390</v>
       </c>
@@ -19008,7 +19027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>391</v>
       </c>
@@ -19054,7 +19073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>392</v>
       </c>
@@ -19100,7 +19119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787">
         <v>393</v>
       </c>
@@ -19146,7 +19165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>394</v>
       </c>
@@ -19192,7 +19211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>395</v>
       </c>
@@ -19238,7 +19257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>396</v>
       </c>
@@ -19284,7 +19303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>397</v>
       </c>
@@ -19330,7 +19349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>398</v>
       </c>
@@ -19376,7 +19395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>399</v>
       </c>
@@ -19422,7 +19441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>400</v>
       </c>
@@ -19468,7 +19487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>401</v>
       </c>
@@ -19514,7 +19533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>402</v>
       </c>
@@ -19560,7 +19579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807">
         <v>403</v>
       </c>
@@ -19606,7 +19625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809">
         <v>404</v>
       </c>
@@ -19652,7 +19671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811">
         <v>405</v>
       </c>
@@ -19698,7 +19717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813">
         <v>406</v>
       </c>
@@ -19744,7 +19763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815">
         <v>407</v>
       </c>
@@ -19790,7 +19809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817">
         <v>408</v>
       </c>
@@ -19836,7 +19855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819">
         <v>409</v>
       </c>
@@ -19882,7 +19901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821">
         <v>410</v>
       </c>
@@ -19928,7 +19947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823">
         <v>411</v>
       </c>
@@ -19974,7 +19993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>412</v>
       </c>
@@ -20020,7 +20039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827">
         <v>413</v>
       </c>
@@ -20066,7 +20085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>414</v>
       </c>
@@ -20112,7 +20131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831">
         <v>415</v>
       </c>
@@ -20158,7 +20177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833">
         <v>416</v>
       </c>
@@ -20204,7 +20223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835">
         <v>417</v>
       </c>
@@ -20250,7 +20269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837">
         <v>418</v>
       </c>
@@ -20296,7 +20315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839">
         <v>419</v>
       </c>
@@ -20342,7 +20361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841">
         <v>420</v>
       </c>
@@ -20388,7 +20407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843">
         <v>421</v>
       </c>
@@ -20434,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845">
         <v>422</v>
       </c>
@@ -20480,7 +20499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847">
         <v>423</v>
       </c>
@@ -20526,7 +20545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849">
         <v>424</v>
       </c>
@@ -20572,7 +20591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851">
         <v>425</v>
       </c>
@@ -20618,7 +20637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853">
         <v>426</v>
       </c>
@@ -20664,7 +20683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855">
         <v>427</v>
       </c>
@@ -20710,7 +20729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857">
         <v>428</v>
       </c>
@@ -20756,7 +20775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>429</v>
       </c>
@@ -20802,7 +20821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861">
         <v>430</v>
       </c>
@@ -20848,7 +20867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863">
         <v>431</v>
       </c>
@@ -20894,7 +20913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865">
         <v>432</v>
       </c>
@@ -20940,7 +20959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>433</v>
       </c>
@@ -20986,7 +21005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869">
         <v>434</v>
       </c>
@@ -21032,7 +21051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871">
         <v>435</v>
       </c>
@@ -21078,7 +21097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873">
         <v>436</v>
       </c>
@@ -21124,7 +21143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>437</v>
       </c>
@@ -21170,7 +21189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>438</v>
       </c>
@@ -21216,7 +21235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879">
         <v>439</v>
       </c>
@@ -21262,7 +21281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881">
         <v>440</v>
       </c>
@@ -21308,7 +21327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883">
         <v>441</v>
       </c>
@@ -21354,7 +21373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>442</v>
       </c>
@@ -21400,7 +21419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887">
         <v>443</v>
       </c>
@@ -21446,7 +21465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889">
         <v>444</v>
       </c>
@@ -21492,7 +21511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891">
         <v>445</v>
       </c>
@@ -21538,7 +21557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893">
         <v>446</v>
       </c>
@@ -21584,7 +21603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895">
         <v>447</v>
       </c>
@@ -21630,7 +21649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897">
         <v>448</v>
       </c>
@@ -21676,7 +21695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899">
         <v>449</v>
       </c>
@@ -21722,7 +21741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901">
         <v>450</v>
       </c>
@@ -21768,7 +21787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="903" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903">
         <v>451</v>
       </c>
@@ -21814,7 +21833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="905" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905">
         <v>452</v>
       </c>
@@ -21860,7 +21879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="907" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907">
         <v>453</v>
       </c>
@@ -21906,7 +21925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909">
         <v>454</v>
       </c>
@@ -21952,7 +21971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="911" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911">
         <v>455</v>
       </c>
@@ -21998,7 +22017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913">
         <v>456</v>
       </c>
@@ -22044,7 +22063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915">
         <v>457</v>
       </c>
@@ -22090,7 +22109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917">
         <v>458</v>
       </c>
@@ -22136,7 +22155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="919" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919">
         <v>459</v>
       </c>
@@ -22182,7 +22201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921">
         <v>460</v>
       </c>
@@ -22228,7 +22247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923">
         <v>461</v>
       </c>
@@ -22274,7 +22293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925">
         <v>462</v>
       </c>
@@ -22320,7 +22339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927">
         <v>463</v>
       </c>
@@ -22366,7 +22385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="929" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929">
         <v>464</v>
       </c>
@@ -22412,7 +22431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931">
         <v>465</v>
       </c>
@@ -22458,7 +22477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933">
         <v>466</v>
       </c>
@@ -22504,7 +22523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935">
         <v>467</v>
       </c>
@@ -22550,7 +22569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="937" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937">
         <v>468</v>
       </c>
@@ -22596,7 +22615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939">
         <v>469</v>
       </c>
@@ -22642,7 +22661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="941" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941">
         <v>470</v>
       </c>
@@ -22688,7 +22707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="943" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943">
         <v>471</v>
       </c>
@@ -22734,7 +22753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="945" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945">
         <v>472</v>
       </c>
@@ -22780,7 +22799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="947" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947">
         <v>473</v>
       </c>
@@ -22826,7 +22845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="949" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949">
         <v>474</v>
       </c>
@@ -22872,7 +22891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="951" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951">
         <v>475</v>
       </c>
@@ -22918,7 +22937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="953" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953">
         <v>476</v>
       </c>
@@ -22964,7 +22983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955">
         <v>477</v>
       </c>
@@ -23010,7 +23029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957">
         <v>478</v>
       </c>
@@ -23056,7 +23075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959">
         <v>479</v>
       </c>
@@ -23102,7 +23121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="961" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961">
         <v>480</v>
       </c>
@@ -23148,7 +23167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963">
         <v>481</v>
       </c>
@@ -23194,7 +23213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="965" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965">
         <v>482</v>
       </c>
@@ -23240,7 +23259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="967" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967">
         <v>483</v>
       </c>
@@ -23286,7 +23305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="969" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969">
         <v>484</v>
       </c>
@@ -23332,7 +23351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="971" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971">
         <v>485</v>
       </c>
@@ -23378,7 +23397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="973" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973">
         <v>486</v>
       </c>
@@ -23424,7 +23443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="975" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975">
         <v>487</v>
       </c>
@@ -23470,7 +23489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="977" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977">
         <v>488</v>
       </c>
@@ -23516,7 +23535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="979" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979">
         <v>489</v>
       </c>
@@ -23562,7 +23581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="981" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981">
         <v>490</v>
       </c>
@@ -23608,7 +23627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="983" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983">
         <v>491</v>
       </c>
@@ -23654,7 +23673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="985" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985">
         <v>492</v>
       </c>
@@ -23700,7 +23719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="987" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987">
         <v>493</v>
       </c>
@@ -23746,7 +23765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="989" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989">
         <v>494</v>
       </c>
@@ -23792,7 +23811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="991" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991">
         <v>495</v>
       </c>
@@ -23838,7 +23857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="993" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993">
         <v>496</v>
       </c>
@@ -23884,7 +23903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="995" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995">
         <v>497</v>
       </c>
@@ -23930,7 +23949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="997" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997">
         <v>498</v>
       </c>
@@ -23976,7 +23995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="999" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999">
         <v>499</v>
       </c>
@@ -24022,7 +24041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001">
         <v>500</v>
       </c>
@@ -24068,7 +24087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003">
         <v>501</v>
       </c>
@@ -24114,7 +24133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005">
         <v>502</v>
       </c>
@@ -24160,7 +24179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1007" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007">
         <v>503</v>
       </c>
@@ -24206,7 +24225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1009" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009">
         <v>504</v>
       </c>
@@ -24252,7 +24271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1011" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011">
         <v>505</v>
       </c>
@@ -24298,7 +24317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1013" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013">
         <v>506</v>
       </c>
@@ -24344,7 +24363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1015" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015">
         <v>507</v>
       </c>
@@ -24390,7 +24409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1017" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017">
         <v>508</v>
       </c>
@@ -24436,7 +24455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1019" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019">
         <v>509</v>
       </c>
@@ -24482,7 +24501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021">
         <v>510</v>
       </c>
@@ -24528,7 +24547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1023" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023">
         <v>511</v>
       </c>
@@ -24574,7 +24593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025">
         <v>512</v>
       </c>
@@ -24620,7 +24639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027">
         <v>513</v>
       </c>
@@ -24666,7 +24685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1029" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029">
         <v>514</v>
       </c>
@@ -24712,7 +24731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1031" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031">
         <v>515</v>
       </c>
@@ -24758,7 +24777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033">
         <v>516</v>
       </c>
@@ -24804,7 +24823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1035" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035">
         <v>517</v>
       </c>
@@ -24850,7 +24869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037">
         <v>518</v>
       </c>
@@ -24896,7 +24915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1039" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039">
         <v>519</v>
       </c>
@@ -24942,7 +24961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1041" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041">
         <v>520</v>
       </c>
@@ -24988,7 +25007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1043" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043">
         <v>521</v>
       </c>
@@ -25034,7 +25053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1045" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045">
         <v>522</v>
       </c>
@@ -25080,7 +25099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1047" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047">
         <v>523</v>
       </c>
@@ -25126,7 +25145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1049" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049">
         <v>524</v>
       </c>
@@ -25172,7 +25191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1051" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051">
         <v>525</v>
       </c>
@@ -25218,7 +25237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1053" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053">
         <v>526</v>
       </c>
@@ -25264,7 +25283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1055" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055">
         <v>527</v>
       </c>
@@ -25310,7 +25329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1057" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057">
         <v>528</v>
       </c>
@@ -25356,7 +25375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1059" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1059">
         <v>529</v>
       </c>
@@ -25402,7 +25421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1061" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1061">
         <v>530</v>
       </c>
@@ -25448,7 +25467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1063" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1063">
         <v>531</v>
       </c>
@@ -25494,7 +25513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1065" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1065">
         <v>532</v>
       </c>
@@ -25540,7 +25559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1067" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067">
         <v>533</v>
       </c>
@@ -25586,7 +25605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1069">
         <v>534</v>
       </c>
@@ -25632,7 +25651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1071">
         <v>535</v>
       </c>
@@ -25678,7 +25697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1073" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1073">
         <v>536</v>
       </c>
@@ -25724,7 +25743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1075">
         <v>537</v>
       </c>
@@ -25770,7 +25789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1077" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1077">
         <v>538</v>
       </c>
@@ -25816,7 +25835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1079">
         <v>539</v>
       </c>
@@ -25862,7 +25881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1081" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081">
         <v>540</v>
       </c>
@@ -25908,7 +25927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1083" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1083">
         <v>541</v>
       </c>
@@ -25954,7 +25973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1085" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1085">
         <v>542</v>
       </c>
@@ -26000,7 +26019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1087" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1087">
         <v>543</v>
       </c>
@@ -26046,7 +26065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1089" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1089">
         <v>544</v>
       </c>
@@ -26092,7 +26111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1091" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1091">
         <v>545</v>
       </c>
@@ -26138,7 +26157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1093" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093">
         <v>546</v>
       </c>
@@ -26184,7 +26203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095">
         <v>547</v>
       </c>
@@ -26230,7 +26249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097">
         <v>548</v>
       </c>
@@ -26276,7 +26295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099">
         <v>549</v>
       </c>
@@ -26322,7 +26341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101">
         <v>550</v>
       </c>
@@ -26368,7 +26387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103">
         <v>551</v>
       </c>
@@ -26414,7 +26433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1105">
         <v>552</v>
       </c>
@@ -26460,7 +26479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107">
         <v>553</v>
       </c>
@@ -26506,7 +26525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1109">
         <v>554</v>
       </c>
@@ -26552,7 +26571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111">
         <v>555</v>
       </c>
@@ -26598,7 +26617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1113">
         <v>556</v>
       </c>
@@ -26644,7 +26663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1115">
         <v>557</v>
       </c>
@@ -26690,7 +26709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117">
         <v>558</v>
       </c>
@@ -26736,7 +26755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1119">
         <v>559</v>
       </c>
@@ -26782,7 +26801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121">
         <v>560</v>
       </c>
@@ -26828,7 +26847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1123">
         <v>561</v>
       </c>
@@ -26874,7 +26893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1125">
         <v>562</v>
       </c>
@@ -26920,7 +26939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1127">
         <v>563</v>
       </c>
@@ -26966,7 +26985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1129">
         <v>564</v>
       </c>
@@ -27012,7 +27031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131">
         <v>565</v>
       </c>
@@ -27058,7 +27077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1133">
         <v>566</v>
       </c>
@@ -27104,7 +27123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135">
         <v>567</v>
       </c>
@@ -27150,7 +27169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137">
         <v>568</v>
       </c>
@@ -27196,7 +27215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1139">
         <v>569</v>
       </c>
@@ -27242,7 +27261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141">
         <v>570</v>
       </c>
@@ -27288,7 +27307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1143">
         <v>571</v>
       </c>
@@ -27334,7 +27353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145">
         <v>572</v>
       </c>
@@ -27380,7 +27399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1147">
         <v>573</v>
       </c>
@@ -27426,7 +27445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1149">
         <v>574</v>
       </c>
@@ -27472,7 +27491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1151">
         <v>575</v>
       </c>
@@ -27518,7 +27537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1153">
         <v>576</v>
       </c>
@@ -27564,7 +27583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1155">
         <v>577</v>
       </c>
@@ -27610,7 +27629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1157">
         <v>578</v>
       </c>
@@ -27656,7 +27675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1159">
         <v>579</v>
       </c>
@@ -27702,7 +27721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1161">
         <v>580</v>
       </c>
@@ -27748,7 +27767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1163">
         <v>581</v>
       </c>
@@ -27794,7 +27813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1165">
         <v>582</v>
       </c>
@@ -27840,7 +27859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1167">
         <v>583</v>
       </c>
@@ -27886,7 +27905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1169">
         <v>584</v>
       </c>
@@ -27932,7 +27951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1171">
         <v>585</v>
       </c>
@@ -27978,7 +27997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1173">
         <v>586</v>
       </c>
@@ -28024,7 +28043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1175">
         <v>587</v>
       </c>
@@ -28070,7 +28089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1177">
         <v>588</v>
       </c>
@@ -28116,7 +28135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1179">
         <v>589</v>
       </c>
@@ -28162,7 +28181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1181">
         <v>590</v>
       </c>
@@ -28208,7 +28227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1183">
         <v>591</v>
       </c>
@@ -28254,7 +28273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1185">
         <v>592</v>
       </c>
@@ -28300,7 +28319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1187">
         <v>593</v>
       </c>
@@ -28346,7 +28365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1189">
         <v>594</v>
       </c>
@@ -28392,7 +28411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1191">
         <v>595</v>
       </c>
@@ -28438,7 +28457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1193">
         <v>596</v>
       </c>
@@ -28484,7 +28503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1195">
         <v>597</v>
       </c>
@@ -28530,7 +28549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1197">
         <v>598</v>
       </c>
@@ -28576,7 +28595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1199">
         <v>599</v>
       </c>
@@ -28622,7 +28641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1201">
         <v>600</v>
       </c>
@@ -28668,7 +28687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1203">
         <v>601</v>
       </c>
@@ -28714,7 +28733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1205">
         <v>602</v>
       </c>
@@ -28760,7 +28779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1207">
         <v>603</v>
       </c>
@@ -28806,7 +28825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1209">
         <v>604</v>
       </c>
@@ -28852,7 +28871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1211">
         <v>605</v>
       </c>
@@ -28898,7 +28917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213">
         <v>606</v>
       </c>
@@ -28944,7 +28963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215">
         <v>607</v>
       </c>
@@ -28990,7 +29009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1217">
         <v>608</v>
       </c>
@@ -29036,7 +29055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1219">
         <v>609</v>
       </c>
@@ -29082,7 +29101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1221">
         <v>610</v>
       </c>
@@ -29128,7 +29147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1223">
         <v>611</v>
       </c>
@@ -29174,7 +29193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1225">
         <v>612</v>
       </c>
@@ -29220,7 +29239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1227">
         <v>613</v>
       </c>
@@ -29266,7 +29285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1229">
         <v>614</v>
       </c>
@@ -29312,7 +29331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1231">
         <v>615</v>
       </c>
@@ -29358,7 +29377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1233">
         <v>616</v>
       </c>
@@ -29404,7 +29423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1235">
         <v>617</v>
       </c>
@@ -29450,7 +29469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1237">
         <v>618</v>
       </c>
@@ -29496,7 +29515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1239">
         <v>619</v>
       </c>
@@ -29542,7 +29561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1241">
         <v>620</v>
       </c>
@@ -29588,7 +29607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1243">
         <v>621</v>
       </c>
@@ -29634,7 +29653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1245">
         <v>622</v>
       </c>
@@ -29680,7 +29699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1247">
         <v>623</v>
       </c>
@@ -29726,7 +29745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1249">
         <v>624</v>
       </c>
@@ -29772,7 +29791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1251">
         <v>625</v>
       </c>
@@ -29818,7 +29837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1253">
         <v>626</v>
       </c>
@@ -29864,7 +29883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1255">
         <v>627</v>
       </c>
@@ -29910,7 +29929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1257">
         <v>628</v>
       </c>
@@ -29956,7 +29975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1259">
         <v>629</v>
       </c>
@@ -30002,7 +30021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1261">
         <v>630</v>
       </c>
@@ -30048,7 +30067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1263">
         <v>631</v>
       </c>
@@ -30094,7 +30113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1265">
         <v>632</v>
       </c>
@@ -30140,7 +30159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1267">
         <v>633</v>
       </c>
@@ -30186,7 +30205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1269">
         <v>634</v>
       </c>
@@ -30232,7 +30251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1271">
         <v>635</v>
       </c>
@@ -30278,7 +30297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1273">
         <v>636</v>
       </c>
@@ -30324,7 +30343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1275">
         <v>637</v>
       </c>
@@ -30370,7 +30389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1277">
         <v>638</v>
       </c>
@@ -30416,7 +30435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1279">
         <v>639</v>
       </c>
@@ -30462,7 +30481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1281">
         <v>640</v>
       </c>
@@ -30508,7 +30527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1283">
         <v>641</v>
       </c>
@@ -30554,7 +30573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1285">
         <v>642</v>
       </c>
@@ -30600,7 +30619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1287">
         <v>643</v>
       </c>
@@ -30646,7 +30665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1289">
         <v>644</v>
       </c>
@@ -30692,7 +30711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1291">
         <v>645</v>
       </c>
@@ -30738,7 +30757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1293">
         <v>646</v>
       </c>
@@ -30784,7 +30803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1295">
         <v>647</v>
       </c>
@@ -30830,7 +30849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1297">
         <v>648</v>
       </c>
@@ -30876,7 +30895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1299">
         <v>649</v>
       </c>
@@ -30922,7 +30941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1301">
         <v>650</v>
       </c>
@@ -30968,7 +30987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1303">
         <v>651</v>
       </c>
@@ -31014,7 +31033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1305">
         <v>652</v>
       </c>
@@ -31060,7 +31079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1307">
         <v>653</v>
       </c>
@@ -31106,7 +31125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1309">
         <v>654</v>
       </c>
@@ -31152,7 +31171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1311">
         <v>655</v>
       </c>
@@ -31198,7 +31217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1313">
         <v>656</v>
       </c>
@@ -31244,7 +31263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1315">
         <v>657</v>
       </c>
@@ -31290,7 +31309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1317">
         <v>658</v>
       </c>
@@ -31336,7 +31355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1319">
         <v>659</v>
       </c>
@@ -31382,7 +31401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1321">
         <v>660</v>
       </c>
@@ -31428,7 +31447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1323">
         <v>661</v>
       </c>
@@ -31474,7 +31493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1325">
         <v>662</v>
       </c>
@@ -31520,7 +31539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1327">
         <v>663</v>
       </c>
@@ -31566,7 +31585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1329">
         <v>664</v>
       </c>
@@ -31612,7 +31631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1331">
         <v>665</v>
       </c>
@@ -31658,7 +31677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1333">
         <v>666</v>
       </c>
@@ -31704,7 +31723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1335">
         <v>667</v>
       </c>
@@ -31750,7 +31769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1337">
         <v>668</v>
       </c>
@@ -31796,7 +31815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1339">
         <v>669</v>
       </c>
@@ -31842,7 +31861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1341">
         <v>670</v>
       </c>
@@ -31888,7 +31907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1343">
         <v>671</v>
       </c>
@@ -31934,7 +31953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1345">
         <v>672</v>
       </c>
@@ -31980,7 +31999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1347">
         <v>673</v>
       </c>
@@ -32026,7 +32045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1349">
         <v>674</v>
       </c>
@@ -32072,7 +32091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1351">
         <v>675</v>
       </c>
@@ -32118,7 +32137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1353">
         <v>676</v>
       </c>
@@ -32164,7 +32183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1355">
         <v>677</v>
       </c>
@@ -32210,7 +32229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1357">
         <v>678</v>
       </c>
@@ -32256,7 +32275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1359">
         <v>679</v>
       </c>
@@ -32302,7 +32321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1361">
         <v>680</v>
       </c>
@@ -32348,7 +32367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1363">
         <v>681</v>
       </c>
@@ -32394,7 +32413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1365">
         <v>682</v>
       </c>
@@ -32440,7 +32459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1367">
         <v>683</v>
       </c>
@@ -32486,7 +32505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1369">
         <v>684</v>
       </c>
@@ -32532,7 +32551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1371">
         <v>685</v>
       </c>
@@ -32578,7 +32597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1373">
         <v>686</v>
       </c>
@@ -32624,7 +32643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1375">
         <v>687</v>
       </c>
@@ -32670,7 +32689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1377">
         <v>688</v>
       </c>
@@ -32716,7 +32735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1379">
         <v>689</v>
       </c>
@@ -32762,7 +32781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1381">
         <v>690</v>
       </c>
@@ -32808,7 +32827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1383">
         <v>691</v>
       </c>
@@ -32854,7 +32873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1385">
         <v>692</v>
       </c>
@@ -32900,7 +32919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1387">
         <v>693</v>
       </c>
@@ -32946,7 +32965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1389">
         <v>694</v>
       </c>
@@ -32992,7 +33011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1391">
         <v>695</v>
       </c>
@@ -33038,7 +33057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1393">
         <v>696</v>
       </c>
@@ -33084,7 +33103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1395">
         <v>697</v>
       </c>
@@ -33130,7 +33149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1397">
         <v>698</v>
       </c>
@@ -33176,7 +33195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1399">
         <v>699</v>
       </c>
@@ -33222,7 +33241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1401">
         <v>700</v>
       </c>
@@ -33268,7 +33287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1403">
         <v>701</v>
       </c>
@@ -33314,7 +33333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1405">
         <v>702</v>
       </c>
@@ -33360,7 +33379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1407">
         <v>703</v>
       </c>
@@ -33406,7 +33425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1409">
         <v>704</v>
       </c>
@@ -33452,7 +33471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1411">
         <v>705</v>
       </c>
@@ -33498,7 +33517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1413">
         <v>706</v>
       </c>
@@ -33544,7 +33563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1415">
         <v>707</v>
       </c>
@@ -33590,7 +33609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1417">
         <v>708</v>
       </c>
@@ -33636,7 +33655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1419">
         <v>709</v>
       </c>
@@ -33682,7 +33701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1421">
         <v>710</v>
       </c>
@@ -33728,7 +33747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1423">
         <v>711</v>
       </c>
@@ -33774,7 +33793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1425">
         <v>712</v>
       </c>
@@ -33820,7 +33839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1427">
         <v>713</v>
       </c>
@@ -33866,7 +33885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1429">
         <v>714</v>
       </c>
@@ -33912,7 +33931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1431">
         <v>715</v>
       </c>
@@ -33958,7 +33977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1433">
         <v>716</v>
       </c>
@@ -34004,7 +34023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1435">
         <v>717</v>
       </c>
@@ -34050,7 +34069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1437">
         <v>718</v>
       </c>
@@ -34096,7 +34115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1439">
         <v>719</v>
       </c>
@@ -34142,7 +34161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1441">
         <v>720</v>
       </c>
@@ -34188,7 +34207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1443">
         <v>721</v>
       </c>
@@ -34234,7 +34253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1445">
         <v>722</v>
       </c>
@@ -34280,7 +34299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1447">
         <v>723</v>
       </c>
@@ -34326,7 +34345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1449">
         <v>724</v>
       </c>
@@ -34372,7 +34391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1451">
         <v>725</v>
       </c>
@@ -34418,7 +34437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1453">
         <v>726</v>
       </c>
@@ -34464,7 +34483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1455">
         <v>727</v>
       </c>
@@ -34510,7 +34529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1457">
         <v>728</v>
       </c>
@@ -34556,7 +34575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1459">
         <v>729</v>
       </c>
@@ -34602,7 +34621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1461">
         <v>730</v>
       </c>
@@ -34648,7 +34667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1463" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1463">
         <v>731</v>
       </c>
@@ -34694,7 +34713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1465">
         <v>732</v>
       </c>
@@ -34740,7 +34759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1467" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1467">
         <v>733</v>
       </c>
@@ -34786,7 +34805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1469">
         <v>734</v>
       </c>
@@ -34832,7 +34851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1471">
         <v>735</v>
       </c>
@@ -34878,7 +34897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1473">
         <v>736</v>
       </c>
@@ -34924,7 +34943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1475">
         <v>737</v>
       </c>
@@ -34970,7 +34989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1477">
         <v>738</v>
       </c>
@@ -35016,7 +35035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1479">
         <v>739</v>
       </c>
@@ -35062,7 +35081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1481">
         <v>740</v>
       </c>
@@ -35108,7 +35127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1483">
         <v>741</v>
       </c>
@@ -35154,7 +35173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1485">
         <v>742</v>
       </c>
@@ -35200,7 +35219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1487" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1487">
         <v>743</v>
       </c>
@@ -35246,7 +35265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1489">
         <v>744</v>
       </c>
@@ -35292,7 +35311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1491">
         <v>745</v>
       </c>
@@ -35338,7 +35357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1493">
         <v>746</v>
       </c>
@@ -35384,7 +35403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1495">
         <v>747</v>
       </c>
@@ -35430,7 +35449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1497">
         <v>748</v>
       </c>
@@ -35476,7 +35495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1499">
         <v>749</v>
       </c>
@@ -35522,7 +35541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1501">
         <v>750</v>
       </c>
@@ -35568,7 +35587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1503">
         <v>751</v>
       </c>
@@ -35614,7 +35633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1505">
         <v>752</v>
       </c>
@@ -35660,7 +35679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1507">
         <v>753</v>
       </c>
@@ -35706,7 +35725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1509">
         <v>754</v>
       </c>
@@ -35752,7 +35771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1511">
         <v>755</v>
       </c>
@@ -35798,7 +35817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1513">
         <v>756</v>
       </c>
@@ -35844,7 +35863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1515">
         <v>757</v>
       </c>
@@ -35890,7 +35909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1517">
         <v>758</v>
       </c>
@@ -35936,7 +35955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1519">
         <v>759</v>
       </c>
@@ -35982,7 +36001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1521">
         <v>760</v>
       </c>
@@ -36028,7 +36047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1523">
         <v>761</v>
       </c>
@@ -36074,7 +36093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1525">
         <v>762</v>
       </c>
@@ -36120,7 +36139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1527">
         <v>763</v>
       </c>
@@ -36166,7 +36185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1529">
         <v>764</v>
       </c>
@@ -36212,7 +36231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1531">
         <v>765</v>
       </c>
@@ -36258,7 +36277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1533">
         <v>766</v>
       </c>
@@ -36304,7 +36323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1535" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1535">
         <v>767</v>
       </c>
@@ -36350,7 +36369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1537" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1537">
         <v>768</v>
       </c>
@@ -36396,7 +36415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1539">
         <v>769</v>
       </c>
@@ -36442,7 +36461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1541" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1541">
         <v>770</v>
       </c>
@@ -36488,7 +36507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1543">
         <v>771</v>
       </c>
@@ -36534,7 +36553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1545" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1545">
         <v>772</v>
       </c>
@@ -36580,7 +36599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1547" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1547">
         <v>773</v>
       </c>
@@ -36626,7 +36645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1549" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1549">
         <v>774</v>
       </c>
@@ -36672,7 +36691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1551" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1551">
         <v>775</v>
       </c>
@@ -36718,7 +36737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1553" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1553">
         <v>776</v>
       </c>
@@ -36764,7 +36783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1555" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1555">
         <v>777</v>
       </c>
@@ -36810,7 +36829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1557" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1557">
         <v>778</v>
       </c>
@@ -36856,7 +36875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1559" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1559">
         <v>779</v>
       </c>
@@ -36902,7 +36921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1561" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1561">
         <v>780</v>
       </c>
@@ -36948,7 +36967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1563" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1563">
         <v>781</v>
       </c>
@@ -36994,7 +37013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1565" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1565">
         <v>782</v>
       </c>
@@ -37040,7 +37059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1567" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1567" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1567">
         <v>783</v>
       </c>
@@ -37086,7 +37105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1569" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1569">
         <v>784</v>
       </c>
@@ -37132,7 +37151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1571" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1571">
         <v>785</v>
       </c>
@@ -37178,7 +37197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1573" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1573">
         <v>786</v>
       </c>
@@ -37224,7 +37243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1575" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1575">
         <v>787</v>
       </c>
@@ -37270,7 +37289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1577" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1577">
         <v>788</v>
       </c>
@@ -37316,7 +37335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1579" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1579">
         <v>789</v>
       </c>
@@ -37362,7 +37381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1581" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1581">
         <v>790</v>
       </c>
@@ -37408,7 +37427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1583" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1583">
         <v>791</v>
       </c>
@@ -37454,7 +37473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1585" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1585">
         <v>792</v>
       </c>
@@ -37500,7 +37519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1587" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1587">
         <v>793</v>
       </c>
@@ -37546,7 +37565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1589" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1589">
         <v>794</v>
       </c>
@@ -37592,7 +37611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1591" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1591">
         <v>795</v>
       </c>
@@ -37638,7 +37657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1593" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1593">
         <v>796</v>
       </c>
@@ -37684,7 +37703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1595" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1595">
         <v>797</v>
       </c>
@@ -37730,7 +37749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1597" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1597">
         <v>798</v>
       </c>
@@ -37776,7 +37795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1599" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1599">
         <v>799</v>
       </c>
@@ -37822,7 +37841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1601" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1601">
         <v>800</v>
       </c>
@@ -37868,7 +37887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1603" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1603">
         <v>801</v>
       </c>
@@ -37914,7 +37933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1605" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1605">
         <v>802</v>
       </c>
@@ -37960,7 +37979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1607" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1607">
         <v>803</v>
       </c>
@@ -38006,7 +38025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1609" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1609">
         <v>804</v>
       </c>
@@ -38052,7 +38071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1611" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1611">
         <v>805</v>
       </c>
@@ -38098,7 +38117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1613" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1613">
         <v>806</v>
       </c>
@@ -38144,7 +38163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1615" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1615">
         <v>807</v>
       </c>
@@ -38190,7 +38209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1617" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1617">
         <v>808</v>
       </c>
@@ -38236,7 +38255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1619" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1619">
         <v>809</v>
       </c>
@@ -38282,7 +38301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1621" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1621">
         <v>810</v>
       </c>
@@ -38328,7 +38347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1623" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1623">
         <v>811</v>
       </c>
@@ -38374,7 +38393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1625" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1625">
         <v>812</v>
       </c>
@@ -38420,7 +38439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1627" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1627">
         <v>813</v>
       </c>
@@ -38466,7 +38485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1629" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1629">
         <v>814</v>
       </c>
@@ -38512,7 +38531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1631" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1631">
         <v>815</v>
       </c>
@@ -38558,7 +38577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1633" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1633">
         <v>816</v>
       </c>
@@ -38604,7 +38623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1635" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1635">
         <v>817</v>
       </c>
@@ -38650,7 +38669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1637" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1637">
         <v>818</v>
       </c>
@@ -38696,7 +38715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1639" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1639">
         <v>819</v>
       </c>
@@ -38742,7 +38761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1641" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1641">
         <v>820</v>
       </c>
@@ -38788,7 +38807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1643" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1643">
         <v>821</v>
       </c>
@@ -38834,7 +38853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1645" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1645">
         <v>822</v>
       </c>
@@ -38880,7 +38899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1647" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1647">
         <v>823</v>
       </c>
@@ -38926,7 +38945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1649" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1649" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1649">
         <v>824</v>
       </c>
@@ -38972,7 +38991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1651" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1651">
         <v>825</v>
       </c>
@@ -39018,7 +39037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1653" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1653">
         <v>826</v>
       </c>
@@ -39064,7 +39083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1655" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1655">
         <v>827</v>
       </c>
@@ -39110,7 +39129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1657" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1657">
         <v>828</v>
       </c>
@@ -39156,7 +39175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1659" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1659" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1659">
         <v>829</v>
       </c>
@@ -39202,7 +39221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1661" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1661">
         <v>830</v>
       </c>
@@ -39248,7 +39267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1663" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1663" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1663">
         <v>831</v>
       </c>
@@ -39294,7 +39313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1665" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1665" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1665">
         <v>832</v>
       </c>
@@ -39340,7 +39359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1667" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1667" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1667">
         <v>833</v>
       </c>
@@ -39386,7 +39405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1669" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1669" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1669">
         <v>834</v>
       </c>
@@ -39432,7 +39451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1671" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1671" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1671">
         <v>835</v>
       </c>
@@ -39478,7 +39497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1673" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1673" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1673">
         <v>836</v>
       </c>
@@ -39524,7 +39543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1675" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1675">
         <v>837</v>
       </c>
@@ -39570,7 +39589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1677" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1677">
         <v>838</v>
       </c>
@@ -39616,7 +39635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1679" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1679">
         <v>839</v>
       </c>
@@ -39662,7 +39681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1681" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1681" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1681">
         <v>840</v>
       </c>
@@ -39708,7 +39727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1683" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1683">
         <v>841</v>
       </c>
@@ -39754,7 +39773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1685" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1685">
         <v>842</v>
       </c>
@@ -39800,7 +39819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1687" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1687" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1687">
         <v>843</v>
       </c>
@@ -39846,7 +39865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1689" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1689">
         <v>844</v>
       </c>
@@ -39892,7 +39911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1691">
         <v>845</v>
       </c>
@@ -39938,7 +39957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1693" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1693">
         <v>846</v>
       </c>
@@ -39984,7 +40003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1695" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1695">
         <v>847</v>
       </c>
@@ -40030,7 +40049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1697" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1697">
         <v>848</v>
       </c>
@@ -40076,7 +40095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1699" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1699">
         <v>849</v>
       </c>
@@ -40122,7 +40141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1701" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1701" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1701">
         <v>850</v>
       </c>
@@ -40168,7 +40187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1703" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1703" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1703">
         <v>851</v>
       </c>
@@ -40214,7 +40233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1705" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1705" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1705">
         <v>852</v>
       </c>
@@ -40260,7 +40279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1707" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1707" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1707">
         <v>853</v>
       </c>
@@ -40306,7 +40325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1709" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1709" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1709">
         <v>854</v>
       </c>
@@ -40352,7 +40371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1711" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1711" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1711">
         <v>855</v>
       </c>
@@ -40398,7 +40417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1713" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1713">
         <v>856</v>
       </c>
@@ -40444,7 +40463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1715" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1715" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1715">
         <v>857</v>
       </c>
@@ -40490,7 +40509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1717" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1717" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1717">
         <v>858</v>
       </c>
@@ -40536,7 +40555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1719" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1719" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1719">
         <v>859</v>
       </c>
@@ -40582,7 +40601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1721" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1721" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1721">
         <v>860</v>
       </c>
@@ -40628,7 +40647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1723" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1723" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1723">
         <v>861</v>
       </c>
@@ -40674,7 +40693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1725" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1725" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1725">
         <v>862</v>
       </c>
@@ -40720,7 +40739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1727" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1727" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1727">
         <v>863</v>
       </c>
@@ -40766,7 +40785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1729" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1729" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1729">
         <v>864</v>
       </c>
@@ -40812,7 +40831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1731" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1731">
         <v>865</v>
       </c>
@@ -40858,7 +40877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1733" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1733" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1733">
         <v>866</v>
       </c>
@@ -40904,7 +40923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1735" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1735" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1735">
         <v>867</v>
       </c>
@@ -40950,7 +40969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1737" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1737">
         <v>868</v>
       </c>
@@ -40996,7 +41015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1739" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1739" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1739">
         <v>869</v>
       </c>
@@ -41042,7 +41061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1741" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1741" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1741">
         <v>870</v>
       </c>
@@ -41088,7 +41107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1743" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1743" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1743">
         <v>871</v>
       </c>
@@ -41134,7 +41153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1745" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1745" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1745">
         <v>872</v>
       </c>
@@ -41180,7 +41199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1747" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1747" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1747">
         <v>873</v>
       </c>
@@ -41226,7 +41245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1749" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1749" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1749">
         <v>874</v>
       </c>
@@ -41272,7 +41291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1751" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1751">
         <v>875</v>
       </c>
@@ -41318,7 +41337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1753" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1753">
         <v>876</v>
       </c>
@@ -41364,7 +41383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1755" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1755" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1755">
         <v>877</v>
       </c>
@@ -41410,7 +41429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1757" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1757" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1757">
         <v>878</v>
       </c>
@@ -41456,7 +41475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1759" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1759" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1759">
         <v>879</v>
       </c>
@@ -41502,7 +41521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1761" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1761">
         <v>880</v>
       </c>
@@ -41548,7 +41567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1763" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1763">
         <v>881</v>
       </c>
@@ -41594,7 +41613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1765" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1765">
         <v>882</v>
       </c>
@@ -41640,7 +41659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1767" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1767">
         <v>883</v>
       </c>
@@ -41686,7 +41705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1769" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1769" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1769">
         <v>884</v>
       </c>
@@ -41732,7 +41751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1771" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1771">
         <v>885</v>
       </c>
@@ -41778,7 +41797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1773" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1773" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1773">
         <v>886</v>
       </c>
@@ -41824,7 +41843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1775" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1775" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1775">
         <v>887</v>
       </c>
@@ -41870,7 +41889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1777" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1777" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1777">
         <v>888</v>
       </c>
@@ -41916,7 +41935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1779" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1779" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1779">
         <v>889</v>
       </c>
@@ -41962,7 +41981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1781" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1781" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1781">
         <v>890</v>
       </c>
@@ -42008,7 +42027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1783" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1783" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1783">
         <v>891</v>
       </c>
@@ -42054,7 +42073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1785" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1785" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1785">
         <v>892</v>
       </c>
@@ -42100,7 +42119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1787" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1787" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1787">
         <v>893</v>
       </c>
@@ -42146,7 +42165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1789" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1789" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1789">
         <v>894</v>
       </c>
@@ -42192,7 +42211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1791" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1791">
         <v>895</v>
       </c>
@@ -42238,7 +42257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1793" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1793">
         <v>896</v>
       </c>
@@ -42284,7 +42303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1795" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1795">
         <v>897</v>
       </c>
@@ -42330,7 +42349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1797" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1797" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1797">
         <v>898</v>
       </c>
@@ -42376,7 +42395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1799" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1799" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1799">
         <v>899</v>
       </c>
@@ -42422,7 +42441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1801" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1801" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1801">
         <v>900</v>
       </c>
@@ -42468,7 +42487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1803" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1803">
         <v>901</v>
       </c>
@@ -42514,7 +42533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1805" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1805" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1805">
         <v>902</v>
       </c>
@@ -42560,7 +42579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1807" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1807" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1807">
         <v>903</v>
       </c>
@@ -42606,7 +42625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1809" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1809" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1809">
         <v>904</v>
       </c>
@@ -42652,7 +42671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1811" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1811" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1811">
         <v>905</v>
       </c>
@@ -42698,7 +42717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1813" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1813" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1813">
         <v>906</v>
       </c>
@@ -42744,7 +42763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1815" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1815" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1815">
         <v>907</v>
       </c>
@@ -42790,7 +42809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1817" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1817" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1817">
         <v>908</v>
       </c>
@@ -42836,7 +42855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1819" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1819" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1819">
         <v>909</v>
       </c>
@@ -42882,7 +42901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1821" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1821" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1821">
         <v>910</v>
       </c>
@@ -42928,7 +42947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1823" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1823" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1823">
         <v>911</v>
       </c>
@@ -42974,7 +42993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1825" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1825" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1825">
         <v>912</v>
       </c>
@@ -43020,7 +43039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1827" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1827" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1827">
         <v>913</v>
       </c>
@@ -43066,7 +43085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1829" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1829" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1829">
         <v>914</v>
       </c>
@@ -43112,7 +43131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1831" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1831" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1831">
         <v>915</v>
       </c>
@@ -43158,7 +43177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1833" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1833" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1833">
         <v>916</v>
       </c>
@@ -43204,7 +43223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1835" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1835" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1835">
         <v>917</v>
       </c>
@@ -43250,7 +43269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1837" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1837" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1837">
         <v>918</v>
       </c>
@@ -43296,7 +43315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1839" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1839" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1839">
         <v>919</v>
       </c>
@@ -43342,7 +43361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1841" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1841" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1841">
         <v>920</v>
       </c>
@@ -43388,7 +43407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1843" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1843" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1843">
         <v>921</v>
       </c>
@@ -43434,7 +43453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1845" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1845" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1845">
         <v>922</v>
       </c>
@@ -43480,7 +43499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1847" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1847">
         <v>923</v>
       </c>
@@ -43526,7 +43545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1849" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1849" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1849">
         <v>924</v>
       </c>
@@ -43572,7 +43591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1851" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1851">
         <v>925</v>
       </c>
@@ -43618,7 +43637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1853" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1853" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1853">
         <v>926</v>
       </c>
@@ -43664,7 +43683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1855" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1855" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1855">
         <v>927</v>
       </c>
@@ -43710,7 +43729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1857" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1857">
         <v>928</v>
       </c>
@@ -43756,7 +43775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1859" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1859" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1859">
         <v>929</v>
       </c>
@@ -43802,7 +43821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1861" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1861" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1861">
         <v>930</v>
       </c>
@@ -43848,7 +43867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1863" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1863" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1863">
         <v>931</v>
       </c>
@@ -43894,7 +43913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1865" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1865" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1865">
         <v>932</v>
       </c>
@@ -43940,7 +43959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1867" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1867" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1867">
         <v>933</v>
       </c>
@@ -43986,7 +44005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1869" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1869" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1869">
         <v>934</v>
       </c>
@@ -44032,7 +44051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1871" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1871" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1871">
         <v>935</v>
       </c>
@@ -44078,7 +44097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1873" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1873" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1873">
         <v>936</v>
       </c>
@@ -44124,7 +44143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1875" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1875" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1875">
         <v>937</v>
       </c>
@@ -44170,7 +44189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1877" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1877" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1877">
         <v>938</v>
       </c>
@@ -44216,7 +44235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1879" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1879" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1879">
         <v>939</v>
       </c>
@@ -44262,7 +44281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1881" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1881" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1881">
         <v>940</v>
       </c>
@@ -44308,7 +44327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1883" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1883" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1883">
         <v>941</v>
       </c>
@@ -44354,7 +44373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1885" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1885" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1885">
         <v>942</v>
       </c>
@@ -44400,7 +44419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1887" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1887" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1887">
         <v>943</v>
       </c>
@@ -44446,7 +44465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1889" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1889" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1889">
         <v>944</v>
       </c>
@@ -44492,7 +44511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1891" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1891">
         <v>945</v>
       </c>
@@ -44538,7 +44557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1893" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1893" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1893">
         <v>946</v>
       </c>
@@ -44584,7 +44603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1895" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1895" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1895">
         <v>947</v>
       </c>
@@ -44630,7 +44649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1897" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1897" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1897">
         <v>948</v>
       </c>
@@ -44676,7 +44695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1899" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1899" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1899">
         <v>949</v>
       </c>
@@ -44722,7 +44741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1901" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1901" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1901">
         <v>950</v>
       </c>
@@ -44768,7 +44787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1903" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1903" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1903">
         <v>951</v>
       </c>
@@ -44814,7 +44833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1905" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1905" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1905">
         <v>952</v>
       </c>
@@ -44860,7 +44879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1907" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1907" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1907">
         <v>953</v>
       </c>
@@ -44906,7 +44925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1909" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1909" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1909">
         <v>954</v>
       </c>
@@ -44952,7 +44971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1911" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1911" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1911">
         <v>955</v>
       </c>
@@ -44998,7 +45017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1913" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1913" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1913">
         <v>956</v>
       </c>
@@ -45044,7 +45063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1915" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1915" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1915">
         <v>957</v>
       </c>
@@ -45090,7 +45109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1917" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1917" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1917">
         <v>958</v>
       </c>
@@ -45136,7 +45155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1919" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1919" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1919">
         <v>959</v>
       </c>
@@ -45182,7 +45201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1921" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1921" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1921">
         <v>960</v>
       </c>
@@ -45228,7 +45247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1923" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1923" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1923">
         <v>961</v>
       </c>
@@ -45274,7 +45293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1925" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1925" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1925">
         <v>962</v>
       </c>
@@ -45320,7 +45339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1927" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1927" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1927">
         <v>963</v>
       </c>
@@ -45366,7 +45385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1929" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1929" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1929">
         <v>964</v>
       </c>
@@ -45412,7 +45431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1931" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1931" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1931">
         <v>965</v>
       </c>
@@ -45458,7 +45477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1933" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1933" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1933">
         <v>966</v>
       </c>
@@ -45504,7 +45523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1935" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1935" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1935">
         <v>967</v>
       </c>
@@ -45550,7 +45569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1937" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1937" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1937">
         <v>968</v>
       </c>
@@ -45596,7 +45615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1939" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1939" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1939">
         <v>969</v>
       </c>
@@ -45642,7 +45661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1941" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1941" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1941">
         <v>970</v>
       </c>
@@ -45688,7 +45707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1943" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1943" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1943">
         <v>971</v>
       </c>
@@ -45734,7 +45753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1945" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1945" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1945">
         <v>972</v>
       </c>
@@ -45780,7 +45799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1947" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1947" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1947">
         <v>973</v>
       </c>
@@ -45826,7 +45845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1949" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1949" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1949">
         <v>974</v>
       </c>
@@ -45872,7 +45891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1951" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1951" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1951">
         <v>975</v>
       </c>
@@ -45918,7 +45937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1953" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1953" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1953">
         <v>976</v>
       </c>
@@ -45964,7 +45983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1955" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1955" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1955">
         <v>977</v>
       </c>
@@ -46010,7 +46029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1957" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1957" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1957">
         <v>978</v>
       </c>
@@ -46056,7 +46075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1959" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1959">
         <v>979</v>
       </c>
@@ -46102,7 +46121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1961" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1961" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1961">
         <v>980</v>
       </c>
@@ -46148,7 +46167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1963" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1963" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1963">
         <v>981</v>
       </c>
@@ -46194,7 +46213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1965" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1965" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1965">
         <v>982</v>
       </c>
@@ -46240,7 +46259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1967" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1967" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1967">
         <v>983</v>
       </c>
@@ -46286,7 +46305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1969" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1969" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1969">
         <v>984</v>
       </c>
@@ -46332,7 +46351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1971" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1971" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1971">
         <v>985</v>
       </c>
@@ -46378,7 +46397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1973" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1973" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1973">
         <v>986</v>
       </c>
@@ -46424,7 +46443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1975" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1975" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1975">
         <v>987</v>
       </c>
@@ -46470,7 +46489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1977" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1977" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1977">
         <v>988</v>
       </c>
@@ -46516,7 +46535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1979" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1979" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1979">
         <v>989</v>
       </c>
@@ -46562,7 +46581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1981" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1981" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1981">
         <v>990</v>
       </c>
@@ -46608,7 +46627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1983" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1983" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1983">
         <v>991</v>
       </c>
@@ -46654,7 +46673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1985" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1985" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1985">
         <v>992</v>
       </c>
@@ -46700,7 +46719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1987" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1987" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1987">
         <v>993</v>
       </c>
@@ -46746,7 +46765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1989" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1989" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1989">
         <v>994</v>
       </c>
@@ -46792,7 +46811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1991" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1991" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1991">
         <v>995</v>
       </c>
@@ -46838,7 +46857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1993" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1993" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1993">
         <v>996</v>
       </c>
@@ -46884,7 +46903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1995" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1995" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1995">
         <v>997</v>
       </c>
@@ -46930,7 +46949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1997" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1997" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1997">
         <v>998</v>
       </c>
@@ -46976,7 +46995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1999" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1999" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1999">
         <v>999</v>
       </c>
@@ -47022,7 +47041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2001" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2001" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2001">
         <v>1000</v>
       </c>
@@ -47053,19 +47072,24 @@
         <v>0</v>
       </c>
       <c r="C2002">
-        <v>0.68882779999999999</v>
+        <f>SUBTOTAL(9,C1:C2001)</f>
+        <v>654</v>
       </c>
       <c r="D2002">
-        <v>3.2276929999999999</v>
+        <f>SUBTOTAL(9,D1:D2001)</f>
+        <v>3184</v>
       </c>
       <c r="E2002">
-        <v>17.102720000000001</v>
+        <f>SUBTOTAL(9,E1:E2001)</f>
+        <v>13203</v>
       </c>
       <c r="F2002">
-        <v>2.2044489999999999</v>
+        <f>SUBTOTAL(9,F1:F2001)</f>
+        <v>2318</v>
       </c>
       <c r="G2002">
-        <v>0.31042239999999999</v>
+        <f>SUBTOTAL(9,G1:G2001)</f>
+        <v>343</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
